--- a/data-manipulation-scripts/sheets-cleanup/sheets/ARO RODAS 12_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/ARO RODAS 12_02.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>CÓD. BARRA</t>
   </si>
@@ -71,6 +71,9 @@
   </si>
   <si>
     <t xml:space="preserve">ARO RODA IRON TRASEIRA 1.85X18 TITAN150 ESD KS 2014/ FAN125 2009 197026 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -376,7 +379,9 @@
       <c r="C2" s="2">
         <v>2.0</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" s="2">
+        <v>182.0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
@@ -388,7 +393,9 @@
       <c r="C3" s="2">
         <v>8.0</v>
       </c>
-      <c r="D3" s="2"/>
+      <c r="D3" s="2">
+        <v>180.0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
@@ -400,7 +407,9 @@
       <c r="C4" s="2">
         <v>1.0</v>
       </c>
-      <c r="D4" s="2"/>
+      <c r="D4" s="2">
+        <v>172.0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
@@ -412,7 +421,9 @@
       <c r="C5" s="2">
         <v>1.0</v>
       </c>
-      <c r="D5" s="3"/>
+      <c r="D5" s="2">
+        <v>172.0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
@@ -424,7 +435,9 @@
       <c r="C6" s="2">
         <v>1.0</v>
       </c>
-      <c r="D6" s="3"/>
+      <c r="D6" s="2">
+        <v>172.0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
@@ -436,7 +449,9 @@
       <c r="C7" s="2">
         <v>5.0</v>
       </c>
-      <c r="D7" s="3"/>
+      <c r="D7" s="2">
+        <v>172.0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
@@ -467,7 +482,9 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4"/>
+      <c r="A10" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
